--- a/atj_saf/atj_bst/cost_breakdown_df.xlsx
+++ b/atj_saf/atj_bst/cost_breakdown_df.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
